--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/updateMember-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/updateMember-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>Statement: updateMember(memberId: string, data: UpdateMemberInput): Promise&lt;ActionResult&lt;MemberWithUser&gt;&gt; — validates input with Zod, delegates to userService.updateMember(), and returns the updated member wrapped in ActionResult.</t>
   </si>
@@ -167,6 +167,30 @@
   </si>
   <si>
     <t>{ success: false, message: "Validation failed", errors: { email: defined } }</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member "alice@gym.test" (fullName: "Alice Smith") seeded via userService.createMember().
+const data: UpdateMemberInput = { email: "alice@gym.test", fullName: "Alice Renamed" }</t>
+  </si>
+  <si>
+    <t>fullName updated; email unchanged</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via userService.createMember(): alice (alice@gym.test), bob (bob@gym.test).
+First call: updateMember(alice.id, { email: "bob@gym.test" }) → ConflictError.
+const data: UpdateMemberInput = { email: "charlie@gym.test", fullName: "Alice Charlie" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { user: { email: "charlie@gym.test", fullName: "Alice Charlie" } } }</t>
+  </si>
+  <si>
+    <t>alice row updated to charlie@gym.test; bob row unchanged</t>
   </si>
   <si>
     <t>Testing</t>
@@ -854,7 +878,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1023,6 +1047,52 @@
         <v>35</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1051,17 +1121,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1073,40 +1143,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1114,40 +1184,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
